--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260903.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260903.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.63%</t>
+          <t>10.61%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.40%</t>
+          <t>10.43%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.11%</t>
+          <t>8.35%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.58%</t>
+          <t>7.56%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.67%</t>
+          <t>5.64%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.38%</t>
+          <t>4.33%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.97%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.43%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1210,51 +1210,51 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>11,337</t>
+          <t>75,174</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>75,174</t>
+          <t>11,337</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1364,51 +1364,51 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>4,921</t>
+          <t>146,245</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>146,245</t>
+          <t>4,921</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1437,39 +1437,39 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>25,781</t>
+          <t>43,583</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>43,583</t>
+          <t>25,781</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>119,186,840</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
